--- a/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,147 +626,143 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3513
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t xml:space="preserve">297
+</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
+          <t xml:space="preserve">6839
 </t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
@@ -781,147 +777,133 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
+          <t xml:space="preserve">435
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">326
+</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1829
 </t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">2920
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">3266
+</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">566
+</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">780
-</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">94
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="n"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2</t>
@@ -936,49 +918,50 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">48
+13
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">7226
 </t>
         </is>
       </c>
@@ -990,91 +973,91 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">1060
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">596
+          <t xml:space="preserve">528
 </t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -1092,145 +1075,129 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
-</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">324
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">486860108728
+171171808
+</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n"/>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3119
+          <t xml:space="preserve">342
 </t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
+          <t xml:space="preserve">506
 </t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2261
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">732
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">662
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="n"/>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -1248,142 +1215,148 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">2926
 </t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">806
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">369
+</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">965
+</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">206
 </t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>8121</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333
-</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">548
-</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1281
-</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="X8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="Y8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">742
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1398,137 +1371,140 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17836
+          <t xml:space="preserve">7835
 </t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1617
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>014</t>
+          <t xml:space="preserve">9629
+</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
+          <t xml:space="preserve">1308
 </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">543
+          <t xml:space="preserve">679
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">824
+</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2785
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">92926
+</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">188
+</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">945
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556
+          <t xml:space="preserve">496
 </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">1212
+</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">1357
+</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308 10
+          <t xml:space="preserve">22929
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
+          <t xml:space="preserve">1328
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t xml:space="preserve">1335
+</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3891
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="n"/>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -1546,135 +1522,145 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
+          <t xml:space="preserve">367
 </t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">339
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">1 36
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">8190
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">3888
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -1692,143 +1678,134 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4203
+          <t xml:space="preserve">2656
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t xml:space="preserve">3601
+</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
+          <t>2459</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">45
+</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>9949</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">660
+</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">266
 </t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1887
-</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29332
-</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">563
-</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1295
-</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="n"/>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -1846,143 +1823,147 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">22
+191
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9233
+          <t xml:space="preserve">979
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t xml:space="preserve">78
+</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">05
+711
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
+          <t xml:space="preserve">22927
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
@@ -2000,145 +1981,144 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">2727
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2156,145 +2136,139 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">903
 </t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">3607
 </t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">2129
 </t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">973
+</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">273
-</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
+          <t xml:space="preserve">527
 </t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="n"/>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -2310,147 +2284,117 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3408
-</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10060
+</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">09
+</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2467,138 +2411,75 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>53041</t>
+          <t xml:space="preserve">356
+</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15242
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0289
-</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">019
-</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>097</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4900
-</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1524
-</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n"/>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
-</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1763
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">617
+</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="n"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1365
-</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="n"/>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="Y16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3861
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="n"/>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -2616,141 +2497,145 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3062
+          <t xml:space="preserve">15992
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">1529
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1317
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">524
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">3922
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">368
 </t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">361
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">3318
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t xml:space="preserve">337
+</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">1207
+</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1425
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>118</t>
+          <t xml:space="preserve">476
+</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -2768,142 +2653,140 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">34182
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">1364
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">1453
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">467
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t xml:space="preserve">815
+</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -2921,144 +2804,128 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262
+          <t xml:space="preserve">3686
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">2064
 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">76
+</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
-</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="X19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">85
+</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="n"/>
+      <c r="X19" s="2" t="n"/>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3076,145 +2943,141 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
-</t>
+          <t>856</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">662
+1254
+</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">926
+</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2929
+</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">716
-</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="X20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="Y20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3231,48 +3094,49 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3575
+          <t xml:space="preserve">3659
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">2415
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -3284,92 +3148,82 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t xml:space="preserve">73
+</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
+          <t xml:space="preserve">91
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="n"/>
       <c r="AA21" t="inlineStr">
         <is>
           <t>14</t>
@@ -3384,49 +3238,49 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2949
+          <t xml:space="preserve">3408
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3189
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -3438,94 +3292,89 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">000
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
+          <t xml:space="preserve">2126
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">2438
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">7250
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="n"/>
       <c r="AA22" t="inlineStr">
         <is>
           <t>15</t>
@@ -3540,145 +3389,143 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16101
+          <t xml:space="preserve">3993
 </t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150519
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">758
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75
+</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">324
+</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">312
+</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">65
 </t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">984
-</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9728
-</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1227
-</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4940
-</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12529
-</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19116
-</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>39411</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3200
-</t>
-        </is>
-      </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
+          <t xml:space="preserve">2922
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18993
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t xml:space="preserve">46
+</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">723
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="n"/>
       <c r="AA23" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3693,125 +3540,147 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
+          <t xml:space="preserve">7326
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">422999227
+1149 6
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1324
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">563
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">4574532851
+12818
 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11170
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1070
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>489</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">557
+</t>
+        </is>
+      </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">246
+</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
+</t>
+        </is>
+      </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">24
+78
 </t>
         </is>
       </c>
@@ -3829,125 +3698,138 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">575
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">214
+</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t xml:space="preserve">11
+</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">6018
+</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>316</t>
-        </is>
-      </c>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t xml:space="preserve">6541
+</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t xml:space="preserve">158
+</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">408
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">3990
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="n"/>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -3962,147 +3844,141 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450
+          <t xml:space="preserve">067
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">24127
+210
+</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">24
 </t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>9861</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">779717
+1791818
+</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7783
+181186
+</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">44
 </t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">314
-</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">552
-</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="n"/>
       <c r="AA26" t="inlineStr">
         <is>
           <t>17</t>
@@ -4117,147 +3993,132 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>329</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2861
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n"/>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">67
+</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
-        </is>
-      </c>
-      <c r="Z27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">872
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="n"/>
       <c r="AA27" t="inlineStr">
         <is>
           <t>18</t>
@@ -4272,49 +4133,45 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2823
+          <t xml:space="preserve">3220
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">399
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">08
+34
 </t>
         </is>
       </c>
@@ -4326,25 +4183,25 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12201
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
@@ -4356,64 +4213,59 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="Z28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">43
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="n"/>
       <c r="AA28" t="inlineStr">
         <is>
           <t>19</t>
@@ -4428,143 +4280,143 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1402
+          <t xml:space="preserve">2907
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t xml:space="preserve">09
+</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">312
+</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">286
 </t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">737
-</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t xml:space="preserve">818
+</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4582,138 +4434,144 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13635
-</t>
+          <t>865</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15065
+          <t xml:space="preserve">368
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">506
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">229
+</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4895
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>90</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>35451</t>
+          <t xml:space="preserve">272
+</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3445
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t xml:space="preserve">46
+</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4115
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4731,140 +4589,145 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2727
+          <t xml:space="preserve">0566
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">4280
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">966
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">388
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1526
 </t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
+          <t xml:space="preserve">3968
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -4882,137 +4745,145 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2635
+          <t xml:space="preserve">2112
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">452
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">21
+</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">111171
+</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">4826
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">972
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">1409
 </t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t xml:space="preserve">94
+</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">381
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">4417
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
@@ -5030,143 +4901,140 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
+          <t xml:space="preserve">3847
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">46
 </t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1290
-</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">785
+</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">439
 </t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t xml:space="preserve">282
+</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">93
+</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5183,137 +5051,133 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">2423
+</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">49
+</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75
+</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">256
 </t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
-</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">702
-</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">2862 2
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -5331,144 +5195,141 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2844
+          <t xml:space="preserve">3116
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">226
+214
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t xml:space="preserve">723
+</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">858
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="n"/>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -5486,141 +5347,138 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">3534
 </t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">060
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">948
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">302
+</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="n"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">89
+</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="Z36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>25</t>
@@ -5635,140 +5493,144 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8264
+          <t xml:space="preserve">4307
 </t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>00401</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12034446</t>
+          <t xml:space="preserve">210
+</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0444</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t xml:space="preserve">42
+</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4950
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1331
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112879
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3936
+          <t xml:space="preserve">622
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5785,134 +5647,147 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653
+          <t xml:space="preserve">6937
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1287
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">534
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">356
+</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">427
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">537
+</t>
+        </is>
+      </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">792798
+11811
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">3248
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">1368
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t xml:space="preserve">466
+</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">7260
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>05</t>
+          <t xml:space="preserve">82745857727
+12119
+</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5929,133 +5804,140 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">3387
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t xml:space="preserve">36
+</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">412
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">2410
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">3607
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">1431
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">665
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">284
+</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">3922
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">729
+          <t xml:space="preserve">794
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -6073,138 +5955,141 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="n"/>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+111
+</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t xml:space="preserve">990
+</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
+          <t xml:space="preserve">632
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t xml:space="preserve">882
+</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6222,144 +6107,141 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">7924
+265
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">3192
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1292
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">705
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6374,21 +6256,16 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2886
-</t>
-        </is>
-      </c>
+      <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -6400,44 +6277,49 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="n"/>
+          <t xml:space="preserve">99
+</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -6449,63 +6331,70 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t xml:space="preserve">905
+</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>843</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="inlineStr"/>
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>29</t>
@@ -6520,19 +6409,19 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
+          <t xml:space="preserve">2363
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -6544,86 +6433,116 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0196
-</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">395
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">412
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="n"/>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr"/>
-      <c r="X43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8235
+</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3923
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -6641,73 +6560,144 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>77797</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
+          <t xml:space="preserve">722
+</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1038
-</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>3546</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4918
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124612
-</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="n"/>
-      <c r="S44" s="2" t="n"/>
-      <c r="T44" s="2" t="n"/>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">668
+</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">756
+</t>
+        </is>
+      </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr"/>
-      <c r="W44" s="2" t="n"/>
-      <c r="X44" s="2" t="n"/>
-      <c r="Y44" s="2" t="n"/>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">462
+</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">841
+</t>
+        </is>
+      </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -6725,121 +6715,129 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
+          <t xml:space="preserve">3659
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">1060
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">277
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">326
+</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="n"/>
+      <c r="S45" s="2" t="n"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
+          <t xml:space="preserve">621
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">3581
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -6856,95 +6854,145 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">021
+</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7283
+</t>
+        </is>
+      </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">7263
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">987
+</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="n"/>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="n"/>
-      <c r="V46" s="2" t="n"/>
-      <c r="W46" s="2" t="n"/>
+          <t xml:space="preserve">4500
+</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">686
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1442
+</t>
+        </is>
+      </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="2" t="n"/>
-      <c r="Z46" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1725
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="n"/>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -6957,9 +7005,105 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">376
+</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">317
+</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">411
+</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">757
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,143 +626,147 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">3513
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">1227
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">0975
 </t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">1017
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">1330
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">112811
 </t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6839
+          <t xml:space="preserve">1561
 </t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="n"/>
+          <t xml:space="preserve">1743
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1100
+</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
@@ -777,133 +781,146 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">435
+          <t xml:space="preserve">2781
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n"/>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n"/>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1214
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2920
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3266
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="Z5" s="2" t="n"/>
+          <t xml:space="preserve">1920
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2</t>
@@ -918,146 +935,139 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">123680
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-13
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">12063
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">14103
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7226
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">2213
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1251
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">2249
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>413</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">854
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -1075,129 +1085,143 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">486860108728
-171171808
-</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n"/>
+          <t xml:space="preserve">4182
+</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">324
+</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>19444</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">203
+</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">141
+</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">10113
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>461</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">19808
 </t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">13119
 </t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
+          <t xml:space="preserve">1595
 </t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2261
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="2" t="n"/>
+          <t xml:space="preserve">1288
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">732
+</t>
+        </is>
+      </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -1215,145 +1239,145 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2926
+          <t xml:space="preserve">193680
 </t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">1275
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">369
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">2417
 </t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2333
+</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1279
+</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1948
+</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1230
+</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">244
 </t>
         </is>
       </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">742
 </t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1371,140 +1395,85 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7835
-</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1618
-</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9629
-</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1308
-</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">679
-</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">171836
+</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2785
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92926
-</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">4870
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">496
-</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1212
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
+          <t xml:space="preserve">13715
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22929
+          <t xml:space="preserve">9080
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1328
-</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1335
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1901
+</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="n"/>
+      <c r="W9" s="2" t="n"/>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="2" t="n"/>
+          <t xml:space="preserve">10325
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13891
+</t>
+        </is>
+      </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -1522,145 +1491,140 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">367
+          <t xml:space="preserve">23567
 </t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 36
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1974
 </t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1275
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1616
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8190
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3888
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">1778
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -1678,134 +1642,144 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656
-</t>
+          <t>4531</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3601
+          <t xml:space="preserve">3933
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t xml:space="preserve">1266
+</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>181</t>
+          <t xml:space="preserve">1187
+</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1711
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">1004
+</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t xml:space="preserve">332
+</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">1563
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>134</t>
+          <t xml:space="preserve">1221
+</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">2295
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">26551
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
-        </is>
-      </c>
-      <c r="Y11" s="2" t="n"/>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">704
+</t>
+        </is>
+      </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1823,147 +1797,145 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">1418240
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-191
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">2201
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">12203
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-711
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">19580
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">1296
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">1303
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22927
+          <t xml:space="preserve">7132
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -1981,144 +1953,140 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">12301
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">12291
 </t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">2211
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1116
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1213
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1970
+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n"/>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">12291
 </t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">1679
 </t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>332</t>
+          <t xml:space="preserve">1130
+</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">1264
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2727
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -2136,139 +2104,144 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
+          <t xml:space="preserve">18214
 </t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3607
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2129
+          <t xml:space="preserve">10195
 </t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">1801
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">2411
 </t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="n"/>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t xml:space="preserve">1286
+</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -2284,116 +2257,146 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="n"/>
-      <c r="F15" s="2" t="n"/>
-      <c r="G15" s="2" t="n"/>
-      <c r="H15" s="2" t="n"/>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3408
+</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1314
+</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1253
+</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>945</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">10080
 </t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1894
 </t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10060
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">1300
 </t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1300
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
@@ -2409,77 +2412,97 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">356
-</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">325
-</t>
-        </is>
-      </c>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">997
 </t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1545
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
+          <t xml:space="preserve">1921
+</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1864
+</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
       <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="n"/>
-      <c r="Q16" s="2" t="n"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14900
+</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1524
+</t>
+        </is>
+      </c>
       <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="n"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">617
-</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="n"/>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">13310
+</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1763
+</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="n"/>
       <c r="W16" s="2" t="n"/>
-      <c r="X16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="Y16" s="2" t="n"/>
+      <c r="X16" s="2" t="n"/>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13861
+</t>
+        </is>
+      </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">423
 </t>
         </is>
       </c>
@@ -2497,145 +2520,135 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15992
+          <t xml:space="preserve">3062
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1529
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1317
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3922
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">368
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
+          <t xml:space="preserve">905
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3318
+          <t xml:space="preserve">1662
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">337
-</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1207
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1273
+</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">476
+          <t xml:space="preserve">17172
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
@@ -2653,140 +2666,145 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34182
+          <t xml:space="preserve">3325
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1257
 </t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1672
 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="n"/>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10084
+</t>
+        </is>
+      </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">1894
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">1322
 </t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1364
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
+          <t xml:space="preserve">1580
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1453
+          <t xml:space="preserve">2011
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">467
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">12298
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">1776
 </t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -2804,128 +2822,145 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3686
+          <t xml:space="preserve">13262
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1205
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2064
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">136
+</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1209
+</t>
+        </is>
+      </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">1207
+</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">1317
 </t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="n"/>
-      <c r="X19" s="2" t="n"/>
+          <t xml:space="preserve">1257
+</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1242
+</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1292
+</t>
+        </is>
+      </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">1885
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -2943,140 +2978,139 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t xml:space="preserve">12990
+</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>911</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1897
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="n"/>
+          <t xml:space="preserve">315
+</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-1254
-</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">926
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2929
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">22384
 </t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">1716
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1830
 </t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -3094,136 +3128,142 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3659
+          <t xml:space="preserve">13575
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2415
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="n"/>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2128
+</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">10010
 </t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>304</t>
+          <t xml:space="preserve">1010
+</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">1301
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">1631
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1288
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="2" t="n"/>
+          <t xml:space="preserve">1841
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>14</t>
@@ -3238,143 +3278,142 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
+          <t xml:space="preserve">12949
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">15312
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">2188
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n"/>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1691
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">1310
 </t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2438
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250
+          <t xml:space="preserve">12165
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="2" t="n"/>
+          <t xml:space="preserve">888
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>15</t>
@@ -3387,145 +3426,85 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3993
-</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">329
-</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1984
+</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4940
+</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">312
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12529
+</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">13200
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2922
-</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="X23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1796
+</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="n"/>
+      <c r="W23" s="2" t="n"/>
+      <c r="X23" s="2" t="n"/>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
-        </is>
-      </c>
-      <c r="Z23" s="2" t="n"/>
+          <t xml:space="preserve">4220
+</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3540,147 +3519,133 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7326
+          <t xml:space="preserve">3220
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">422999227
-1149 6
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
+          <t xml:space="preserve">1092
 </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1324
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">563
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4574532851
-12818
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1070
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">557
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1249
+</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1279
+</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1640
+</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1238
+</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">1281
 </t>
         </is>
       </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">893
-</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">325
-</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1314
-</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">297
-</t>
-        </is>
-      </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1844
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-78
+          <t xml:space="preserve">553
 </t>
         </is>
       </c>
@@ -3698,138 +3663,141 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">1778
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">575
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6018
-</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6541
+          <t xml:space="preserve">932
 </t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3990
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="2" t="n"/>
+          <t xml:space="preserve">952
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>16</t>
@@ -3844,141 +3812,141 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">067
+          <t xml:space="preserve">23450
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">204
 </t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24127
-210
-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>9861</t>
-        </is>
-      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">779717
-1791818
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">2241
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7783
-181186
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t xml:space="preserve">552
+</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">1236
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>621</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="2" t="n"/>
+          <t xml:space="preserve">1743
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>17</t>
@@ -3993,132 +3961,141 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">24182
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1329
 </t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">2861
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n"/>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n"/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t xml:space="preserve">1990
+</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">042
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1264
 </t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1530
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">2955
 </t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1302
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
-</t>
-        </is>
-      </c>
-      <c r="Z27" s="2" t="n"/>
+          <t xml:space="preserve">1742
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1105
+</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>18</t>
@@ -4133,139 +4110,145 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
+          <t xml:space="preserve">2823
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1326
+</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1184
+</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">499
+</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1980
+</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1297
+</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">251
 </t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">399
-</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-34
-</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1000
-</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">1694
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">12244
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">12603
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="Z28" s="2" t="n"/>
+          <t xml:space="preserve">1860
+</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">143
+</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>19</t>
@@ -4280,143 +4263,144 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>205</t>
+          <t xml:space="preserve">292
+</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1254
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">1737
 </t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">2350
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">1226
+</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">1818
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4432,146 +4416,82 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>865</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">368
-</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">5069
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1922
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">506
-</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1237
+</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">14895
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">853
-</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1210
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="n"/>
+      <c r="R30" s="2" t="n"/>
+      <c r="S30" s="2" t="n"/>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">13445
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1688
+</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="n"/>
+      <c r="W30" s="2" t="n"/>
+      <c r="X30" s="2" t="n"/>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">14115
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
@@ -4589,145 +4509,138 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0566
+          <t xml:space="preserve">2727
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">313
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4280
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">966
+          <t xml:space="preserve">1884
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">388
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1526
+          <t xml:space="preserve">1202
 </t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">1236
 </t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
+          <t xml:space="preserve">1979
 </t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">2042
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1271
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3968
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">638
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
-</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">12067
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -4745,145 +4658,139 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112
+          <t xml:space="preserve">12635
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">452
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111171
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4826
-</t>
+          <t>9901</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1409
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">1698
 </t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">381
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1271
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4417
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -4901,139 +4808,135 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3847
+          <t xml:space="preserve">1441
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">11290
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">2241
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr"/>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">439
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1918
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5051,133 +4954,140 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2423
+          <t xml:space="preserve">11178
 </t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="n"/>
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">11678
 </t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="n"/>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">1301
 </t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">702
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2862 2
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">1625
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5195,141 +5105,138 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
+          <t xml:space="preserve">12844
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">2095
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-214
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1176
 </t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1690
+</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
-</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">2754
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="Y35" s="2" t="n"/>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">858
+</t>
+        </is>
+      </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5347,135 +5254,145 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3534
+          <t xml:space="preserve">11172
 </t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">725
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">060
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="n"/>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
-</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="n"/>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1948
+</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">1214
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -5493,144 +5410,86 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4307
-</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311
-</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">8264
+</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1429
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">975
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1034
+</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1331
+</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="n"/>
+      <c r="S37" s="2" t="n"/>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
+          <t xml:space="preserve">3936
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
-</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1404
+</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="n"/>
+      <c r="W37" s="2" t="n"/>
+      <c r="X37" s="2" t="n"/>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>283</t>
+          <t xml:space="preserve">14160
+</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">1280
+</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5647,146 +5506,135 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6937
+          <t xml:space="preserve">1633
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">534
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">1686
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">356
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">427
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">537
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">792798
-11811
+          <t xml:space="preserve">19273
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3248
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">28111
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1368
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">466
+          <t xml:space="preserve">1225
 </t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260
+          <t xml:space="preserve">18392
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82745857727
-12119
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -5804,140 +5652,145 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3387
+          <t xml:space="preserve">3325
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">1907
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1693
 </t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">935
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3607
+          <t xml:space="preserve">11307
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1431
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">1665
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3922
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">794
+          <t xml:space="preserve">729
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">1061
 </t>
         </is>
       </c>
@@ -5955,71 +5808,73 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">2781
 </t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">1308
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">12297
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t xml:space="preserve">31
+</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t xml:space="preserve">210
+</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-111
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>206</t>
+          <t xml:space="preserve">1246
+</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -6030,66 +5885,67 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">102
+</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1253
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">632
+          <t xml:space="preserve">1654
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">1273
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6107,140 +5963,144 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7924
-265
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3192
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1208
+</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="n"/>
+          <t xml:space="preserve">1209
+</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">1938
 </t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">2093
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1287
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">7205
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">1271
+</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">18411
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -6256,16 +6116,21 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2886
+</t>
+        </is>
+      </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -6277,121 +6142,121 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">11886
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">2912
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">16000
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1309
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1170
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">12071
+</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">12393
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">1818
 </t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -6409,19 +6274,19 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2363
+          <t xml:space="preserve">23116
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -6433,116 +6298,115 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1186
+</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="n"/>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8235
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>354</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">1843
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -6558,149 +6422,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">722
-</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>3546</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">668
-</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">756
-</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">462
-</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="X44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="Y44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">841
-</t>
-        </is>
-      </c>
-      <c r="Z44" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="n"/>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="n"/>
+      <c r="S44" s="2" t="n"/>
+      <c r="T44" s="2" t="n"/>
+      <c r="U44" s="2" t="n"/>
+      <c r="V44" s="2" t="n"/>
+      <c r="W44" s="2" t="n"/>
+      <c r="X44" s="2" t="n"/>
+      <c r="Y44" s="2" t="n"/>
+      <c r="Z44" s="2" t="n"/>
       <c r="AA44" t="inlineStr">
         <is>
           <t>31</t>
@@ -6715,91 +6460,60 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3659
-</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">17227
+</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n"/>
+      <c r="E45" s="2" t="n"/>
+      <c r="F45" s="2" t="n"/>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>061</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">2936
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">1649
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">510
+</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">1918
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">1462
 </t>
         </is>
       </c>
@@ -6807,41 +6521,31 @@
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
+          <t xml:space="preserve">3414
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3581
-</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="X45" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">16680
+</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="n"/>
+      <c r="W45" s="2" t="n"/>
+      <c r="X45" s="2" t="n"/>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="2" t="n"/>
+          <t xml:space="preserve">9923
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1985
+</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6856,143 +6560,141 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">2907
 </t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">021
-</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">1101
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7283
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7263
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">987
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">1984
 </t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4500
+          <t xml:space="preserve">1683
 </t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">12922
 </t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1442
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1725
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="2" t="n"/>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -7003,108 +6705,6 @@
       <c r="B47" t="inlineStr">
         <is>
           <t>Tot.</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">376
-</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">317
-</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">411
-</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
-</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">757
-</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">

--- a/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>335</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -655,43 +655,43 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">2764
 </t>
         </is>
       </c>
@@ -703,7 +703,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1017
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -715,31 +715,31 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112811
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -751,22 +751,17 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1743
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1100
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">17543
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="n"/>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
@@ -787,7 +782,8 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">311
+</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -798,7 +794,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -816,13 +812,13 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -834,36 +830,37 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>05</t>
+          <t xml:space="preserve">254
+</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">0 4
 </t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -875,25 +872,25 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -911,7 +908,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -935,13 +932,13 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123680
+          <t xml:space="preserve">2681
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">814
 </t>
         </is>
       </c>
@@ -953,13 +950,13 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12063
+          <t xml:space="preserve">2635
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14103
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -971,62 +968,68 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n"/>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1251
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">3124
 </t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t xml:space="preserve">273
+</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1037,7 +1040,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
@@ -1049,25 +1052,25 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
+          <t xml:space="preserve">454
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1103,7 +1106,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -1115,24 +1118,25 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19444</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10113
+          <t xml:space="preserve">011
 </t>
         </is>
       </c>
@@ -1150,30 +1154,31 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19808
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13119
+          <t xml:space="preserve">1319
 </t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -1185,13 +1190,13 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1595
+          <t xml:space="preserve">595
 </t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -1239,94 +1244,94 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193680
+          <t xml:space="preserve">96811
 </t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">335
+</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">008
+</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">965
+</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">333
 </t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1218
-</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1275
-</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1221
-</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2417
-</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1965
-</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1019
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2333
-</t>
-        </is>
-      </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">256
@@ -1335,19 +1340,19 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -1365,7 +1370,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
@@ -1395,24 +1400,49 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">171836
-</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="2" t="n"/>
-      <c r="G9" s="2" t="n"/>
-      <c r="H9" s="2" t="n"/>
+          <t xml:space="preserve">11850
+</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1617
+</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1074
+</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13549
+</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54
+</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121008
+</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -1422,9 +1452,24 @@
 </t>
         </is>
       </c>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1094
+</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11080
+</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1282
+</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">4870
@@ -1437,37 +1482,57 @@
 </t>
         </is>
       </c>
-      <c r="Q9" s="2" t="n"/>
-      <c r="R9" s="2" t="n"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1566
+</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1244
+</t>
+        </is>
+      </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13715
+          <t xml:space="preserve">1537905
 </t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9080
+          <t xml:space="preserve">3080
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1901
-</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="n"/>
-      <c r="W9" s="2" t="n"/>
+          <t xml:space="preserve">901
+</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 2 20
+</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14200
+</t>
+        </is>
+      </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10325
+          <t xml:space="preserve">11395
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13891
+          <t xml:space="preserve">5891
 </t>
         </is>
       </c>
@@ -1491,13 +1556,13 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23567
+          <t xml:space="preserve">3567
 </t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">8295
 </t>
         </is>
       </c>
@@ -1509,7 +1574,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -1521,23 +1586,23 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
-</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">42
 </t>
         </is>
       </c>
-      <c r="K10" s="2" t="n"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1175
+</t>
+        </is>
+      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">219
@@ -1558,7 +1623,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1974
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
@@ -1570,19 +1635,19 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -1594,7 +1659,7 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -1606,7 +1671,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
@@ -1618,7 +1683,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
+          <t xml:space="preserve">14178
 </t>
         </is>
       </c>
@@ -1642,36 +1707,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t xml:space="preserve">420
+</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3933
+          <t xml:space="preserve">9353
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
@@ -1683,19 +1749,19 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1711
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">10104
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">2016
 </t>
         </is>
       </c>
@@ -1713,13 +1779,13 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -1737,7 +1803,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -1749,19 +1815,19 @@
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2295
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26551
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -1773,7 +1839,7 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">704
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -1797,94 +1863,94 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418240
+          <t xml:space="preserve">12182
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">828
+</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">328
 </t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1265
-</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1204
-</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2201
-</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12203
-</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">258
@@ -1899,19 +1965,19 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19580
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1296
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
@@ -1929,13 +1995,13 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7132
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
@@ -1953,13 +2019,13 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12301
+          <t xml:space="preserve">2301
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -1971,7 +2037,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -1983,7 +2049,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -1995,74 +2061,79 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1116
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1213
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="n"/>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1679
+          <t xml:space="preserve">679
 </t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
@@ -2080,13 +2151,13 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">8008
 </t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -2104,7 +2175,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18214
+          <t xml:space="preserve">8214
 </t>
         </is>
       </c>
@@ -2116,7 +2187,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -2128,36 +2199,37 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1801
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">1878
 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>08</t>
+          <t xml:space="preserve">08
+</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2411
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2169,31 +2241,31 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">0 4
 </t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -2211,7 +2283,7 @@
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -2229,19 +2301,19 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2265,25 +2337,25 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
@@ -2295,18 +2367,19 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">4080
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10080
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -2318,19 +2391,19 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1894
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -2342,7 +2415,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -2354,7 +2427,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -2366,38 +2439,37 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">7166
 </t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2412,12 +2484,21 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153081
+</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15242
+</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
-</t>
+          <t>992</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2428,19 +2509,19 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1545
+          <t xml:space="preserve">5245
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1921
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -2452,22 +2533,37 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1864
-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
+          <t xml:space="preserve">1624
+</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1022
+</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1101
+</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11290
+</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14900
+          <t xml:space="preserve">4900
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -2477,32 +2573,57 @@
 </t>
         </is>
       </c>
-      <c r="R16" s="2" t="n"/>
-      <c r="S16" s="2" t="n"/>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1257
+</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1427
+</t>
+        </is>
+      </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13310
+          <t xml:space="preserve">3310
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1763
-</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="n"/>
-      <c r="W16" s="2" t="n"/>
-      <c r="X16" s="2" t="n"/>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4126
+</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2512
+</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1400
+</t>
+        </is>
+      </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13861
+          <t xml:space="preserve">138611
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">423
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -2538,13 +2659,13 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -2556,7 +2677,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2566,7 +2687,12 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="2" t="n"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">206
@@ -2581,8 +2707,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2593,25 +2718,25 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">9305
 </t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -2623,32 +2748,37 @@
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">1153
 </t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
-</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr"/>
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17172
+          <t xml:space="preserve">1412
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2666,103 +2796,100 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
-</t>
+          <t>33411</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1192
+</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11714
+</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1697
+</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1294
+</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">970
+</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">322
 </t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1192
-</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1257
-</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1672
-</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">140
-</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10084
-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1894
-</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1970
-</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1322
-</t>
-        </is>
-      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -2774,13 +2901,13 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -2792,19 +2919,19 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12298
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1776
+          <t xml:space="preserve">776
 </t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -2822,19 +2949,19 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13262
+          <t xml:space="preserve">3262
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -2852,7 +2979,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
@@ -2864,37 +2991,37 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -2912,25 +3039,25 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
+          <t xml:space="preserve">2553
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -2948,13 +3075,13 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -2978,18 +3105,19 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12990
+          <t xml:space="preserve">28990
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t xml:space="preserve">297
+</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1897
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -3007,25 +3135,25 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">1884
 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3037,32 +3165,37 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="n"/>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22384
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -3074,7 +3207,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1716
+          <t xml:space="preserve">716
 </t>
         </is>
       </c>
@@ -3098,13 +3231,13 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1830
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
@@ -3128,7 +3261,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13575
+          <t xml:space="preserve">3575
 </t>
         </is>
       </c>
@@ -3140,37 +3273,43 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
+          <t xml:space="preserve">18281
+</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1164
+</t>
+        </is>
+      </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3182,37 +3321,37 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">889
 </t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10010
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1010
+          <t xml:space="preserve">0 0
 </t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -3224,7 +3363,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1631
+          <t xml:space="preserve">631
 </t>
         </is>
       </c>
@@ -3242,7 +3381,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3254,13 +3393,13 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1841
+          <t xml:space="preserve">184841
 </t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">014
 </t>
         </is>
       </c>
@@ -3278,55 +3417,61 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12949
+          <t xml:space="preserve">9929
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15312
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2188
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">250
+</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n"/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1691
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -3344,19 +3489,19 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">108000
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -3374,7 +3519,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
@@ -3386,19 +3531,19 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12165
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -3426,20 +3571,39 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="n"/>
-      <c r="F23" s="2" t="n"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16101
+</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1554
+</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">952
+</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1258
+</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -3454,45 +3618,90 @@
 </t>
         </is>
       </c>
-      <c r="K23" s="2" t="n"/>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1984
-</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="n"/>
-      <c r="N23" s="2" t="n"/>
+          <t xml:space="preserve">984
+</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9 78
+</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16133
+</t>
+        </is>
+      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">4940
 </t>
         </is>
       </c>
-      <c r="P23" s="2" t="n"/>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12529
-</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="n"/>
-      <c r="S23" s="2" t="n"/>
+          <t xml:space="preserve">1529
+</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12406
+</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1153947
+</t>
+        </is>
+      </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13200
+          <t xml:space="preserve">3200
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1796
-</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="n"/>
-      <c r="W23" s="2" t="n"/>
-      <c r="X23" s="2" t="n"/>
+          <t xml:space="preserve">796 1
+</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1223
+</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1406
+</t>
+        </is>
+      </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">4220
@@ -3501,7 +3710,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
@@ -3519,19 +3728,18 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1311
+          <t xml:space="preserve">9311
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1092
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
@@ -3555,15 +3763,20 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="n"/>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1019
+</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -3575,41 +3788,43 @@
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">227
+</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t xml:space="preserve">4
+</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">053
 </t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1640
+          <t xml:space="preserve">640
 </t>
         </is>
       </c>
@@ -3627,26 +3842,25 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">553
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3663,7 +3877,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
@@ -3681,22 +3895,28 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">23
@@ -3705,7 +3925,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -3717,24 +3937,25 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -3752,7 +3973,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -3764,37 +3985,37 @@
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">9 52
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -3812,24 +4033,25 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23450
+          <t xml:space="preserve">8450
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">9317
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t xml:space="preserve">205
+</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
@@ -3841,11 +4063,16 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n"/>
+          <t xml:space="preserve">18868
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">144
@@ -3854,7 +4081,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -3878,7 +4105,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -3890,19 +4117,19 @@
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">3854
 </t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -3920,24 +4147,25 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t xml:space="preserve">268
+</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1743
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
@@ -3961,7 +4189,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24182
+          <t xml:space="preserve">14182
 </t>
         </is>
       </c>
@@ -3973,36 +4201,43 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2861
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">1387
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="n"/>
+          <t xml:space="preserve">1176
+</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t xml:space="preserve">52
+</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4020,19 +4255,19 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">042
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -4044,19 +4279,19 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1264
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530
+          <t xml:space="preserve">530
 </t>
         </is>
       </c>
@@ -4074,25 +4309,25 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2955
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1742
+          <t xml:space="preserve">742
 </t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -4122,7 +4357,8 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -4139,13 +4375,13 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">1884
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4157,7 +4393,8 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>126</t>
+          <t xml:space="preserve">800
+</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -4168,18 +4405,19 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">499
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">231
+</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -4191,7 +4429,7 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
+          <t xml:space="preserve">29798
 </t>
         </is>
       </c>
@@ -4203,37 +4441,37 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12603
+          <t xml:space="preserve">26595
 </t>
         </is>
       </c>
@@ -4245,8 +4483,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4263,7 +4500,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">1221121
 </t>
         </is>
       </c>
@@ -4281,7 +4518,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">2472
 </t>
         </is>
       </c>
@@ -4299,7 +4536,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -4309,12 +4546,7 @@
 </t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
+      <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">219
@@ -4323,30 +4555,31 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">241 9
 </t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">09
+</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -4364,25 +4597,25 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1737
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">2515
 </t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2350
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4394,13 +4627,13 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4416,31 +4649,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6251
+</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">565
+</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11200
+</t>
+        </is>
+      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5069
+          <t xml:space="preserve">5698
 </t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1922
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1148
 </t>
         </is>
       </c>
@@ -4450,42 +4703,87 @@
 </t>
         </is>
       </c>
-      <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="n"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1802
+</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1228
+</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14895
+          <t xml:space="preserve">4895
 </t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="n"/>
-      <c r="R30" s="2" t="n"/>
-      <c r="S30" s="2" t="n"/>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3121
+</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01 35
+</t>
+        </is>
+      </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13445
+          <t xml:space="preserve">3445
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1688
-</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="n"/>
-      <c r="W30" s="2" t="n"/>
-      <c r="X30" s="2" t="n"/>
+          <t xml:space="preserve">688
+</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1274
+</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1153
+</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14115
+          <t xml:space="preserve">4115
 </t>
         </is>
       </c>
@@ -4515,7 +4813,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">212461
 </t>
         </is>
       </c>
@@ -4527,25 +4825,25 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -4555,92 +4853,94 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="2" t="n"/>
+      <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1979
+          <t xml:space="preserve">979
 </t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2042
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">638
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t xml:space="preserve">1255
+</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12067
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t xml:space="preserve">1823
+</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16828
 </t>
         </is>
       </c>
@@ -4658,13 +4958,13 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12635
+          <t xml:space="preserve">2635
 </t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -4676,7 +4976,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -4694,11 +4994,16 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n"/>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">34
@@ -4713,19 +5018,20 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t xml:space="preserve">990
+</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4742,19 +5048,19 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1698
+          <t xml:space="preserve">698
 </t>
         </is>
       </c>
@@ -4766,31 +5072,31 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -4808,7 +5114,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1441
+          <t xml:space="preserve">448
 </t>
         </is>
       </c>
@@ -4832,13 +5138,13 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11290
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -4848,10 +5154,14 @@
 </t>
         </is>
       </c>
-      <c r="J33" s="2" t="n"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
@@ -4869,7 +5179,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -4879,7 +5189,12 @@
 </t>
         </is>
       </c>
-      <c r="P33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">242
@@ -4894,49 +5209,49 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -4954,7 +5269,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11178
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -4966,13 +5281,13 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">24 9
 </t>
         </is>
       </c>
@@ -4984,7 +5299,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11678
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
@@ -4994,7 +5309,7 @@
 </t>
         </is>
       </c>
-      <c r="J34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">59
@@ -5021,25 +5336,25 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -5051,25 +5366,25 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
+          <t xml:space="preserve">802
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -5081,13 +5396,13 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -5105,25 +5420,25 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12844
+          <t xml:space="preserve">2844
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2095
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -5141,12 +5456,13 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t xml:space="preserve">15
+</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5158,19 +5474,25 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
-</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t xml:space="preserve">2189
+</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
@@ -5188,19 +5510,19 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2754
+          <t xml:space="preserve">754
 </t>
         </is>
       </c>
@@ -5224,7 +5546,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">129593
 </t>
         </is>
       </c>
@@ -5236,7 +5558,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">1649
 </t>
         </is>
       </c>
@@ -5278,13 +5600,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -5302,7 +5624,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -5320,19 +5642,19 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -5356,31 +5678,31 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -5392,7 +5714,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -5414,12 +5736,27 @@
 </t>
         </is>
       </c>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1429
+</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11215
+</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
@@ -5431,11 +5768,16 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="n"/>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1179
@@ -5448,23 +5790,48 @@
 </t>
         </is>
       </c>
-      <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2" t="n"/>
-      <c r="O37" s="2" t="n"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1331
-</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="n"/>
-      <c r="S37" s="2" t="n"/>
+          <t xml:space="preserve">2331
+</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1272
+</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1363
+</t>
+        </is>
+      </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3936
@@ -5473,16 +5840,31 @@
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404
-</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="n"/>
-      <c r="W37" s="2" t="n"/>
-      <c r="X37" s="2" t="n"/>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1241
+</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1298
+</t>
+        </is>
+      </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14160
+          <t xml:space="preserve">124660
 </t>
         </is>
       </c>
@@ -5506,7 +5888,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1633
+          <t xml:space="preserve">1553
 </t>
         </is>
       </c>
@@ -5518,7 +5900,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">2 0 0
 </t>
         </is>
       </c>
@@ -5536,18 +5918,28 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1686
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1118
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 1
+</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">207
@@ -5556,7 +5948,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -5568,7 +5960,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -5580,7 +5972,7 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -5592,31 +5984,31 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19273
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">8287
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28111
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -5628,7 +6020,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18392
+          <t xml:space="preserve">1832
 </t>
         </is>
       </c>
@@ -5652,19 +6044,19 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">3320
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1907
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1693
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -5682,7 +6074,7 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -5694,13 +6086,13 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">935
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5724,19 +6116,19 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11307
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -5754,7 +6146,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1665
+          <t xml:space="preserve">66853
 </t>
         </is>
       </c>
@@ -5766,7 +6158,7 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">2 78
 </t>
         </is>
       </c>
@@ -5778,7 +6170,7 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">2178
 </t>
         </is>
       </c>
@@ -5790,7 +6182,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1061
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -5808,7 +6200,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
+          <t xml:space="preserve">2788
 </t>
         </is>
       </c>
@@ -5826,19 +6218,19 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12297
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
@@ -5850,13 +6242,13 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5868,12 +6260,13 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -5885,19 +6278,19 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
+          <t xml:space="preserve">807
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1253
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -5909,19 +6302,19 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1654
+          <t xml:space="preserve">654
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -5933,7 +6326,7 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1273
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
@@ -5945,7 +6338,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">18114
 </t>
         </is>
       </c>
@@ -5963,7 +6356,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">2486
 </t>
         </is>
       </c>
@@ -5975,7 +6368,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
@@ -5987,7 +6380,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5999,7 +6392,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -6011,19 +6404,19 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
@@ -6035,7 +6428,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1938
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
@@ -6047,7 +6440,7 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2093
+          <t xml:space="preserve">2953
 </t>
         </is>
       </c>
@@ -6059,51 +6452,47 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7205
+          <t xml:space="preserve">805
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18411
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1811
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr"/>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -6148,25 +6537,25 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11886
+          <t xml:space="preserve">1886
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6178,7 +6567,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2912
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -6190,49 +6579,49 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1309
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1170
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12071
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
@@ -6244,7 +6633,7 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12393
+          <t xml:space="preserve">189535
 </t>
         </is>
       </c>
@@ -6274,7 +6663,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23116
+          <t xml:space="preserve">3126
 </t>
         </is>
       </c>
@@ -6286,7 +6675,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">9210
 </t>
         </is>
       </c>
@@ -6308,7 +6697,12 @@
 </t>
         </is>
       </c>
-      <c r="I43" s="2" t="n"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1416
+</t>
+        </is>
+      </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">30
@@ -6329,49 +6723,49 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">770
 </t>
         </is>
       </c>
@@ -6383,7 +6777,7 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -6395,18 +6789,18 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>958</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1843
+          <t xml:space="preserve">18495
 </t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -6422,7 +6816,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="n"/>
       <c r="E44" s="2" t="n"/>
       <c r="F44" s="2" t="n"/>
@@ -6460,27 +6859,42 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17227
-</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="n"/>
-      <c r="E45" s="2" t="n"/>
-      <c r="F45" s="2" t="n"/>
+          <t xml:space="preserve">14234
+</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9227
+</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101011
+</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>061</t>
+          <t xml:space="preserve">121010
+</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2936
+          <t xml:space="preserve">936
 </t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">025
 </t>
         </is>
       </c>
@@ -6492,33 +6906,53 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="n"/>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1009001604
+</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="n"/>
-      <c r="N45" s="2" t="n"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161285
+</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
+          <t xml:space="preserve">49160
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1462
-</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="n"/>
-      <c r="S45" s="2" t="n"/>
+          <t xml:space="preserve">12463
+</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1222
+</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
+        </is>
+      </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">3414
@@ -6527,22 +6961,36 @@
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16680
-</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="n"/>
-      <c r="W45" s="2" t="n"/>
-      <c r="X45" s="2" t="n"/>
+          <t xml:space="preserve">66 8
+</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2220
+</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14124
+</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1225
+</t>
+        </is>
+      </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9923
-</t>
+          <t>39831</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1985
+          <t xml:space="preserve">108209
 </t>
         </is>
       </c>
@@ -6566,13 +7014,14 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">1305
 </t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -6583,115 +7032,121 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 5
+</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">984
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2717
+</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1152
+</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1268
+</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2738
+</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1285
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1206
-</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1984
-</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1293
-</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>6451</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1277
-</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1683
-</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12922
-</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1238
-</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1226
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>336</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
@@ -691,7 +691,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2764
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -703,8 +703,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>061</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -721,7 +720,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
@@ -751,13 +750,13 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">2921
 </t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17543
+          <t xml:space="preserve">743
 </t>
         </is>
       </c>
@@ -812,13 +811,13 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -836,7 +835,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
@@ -878,7 +877,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -902,7 +901,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -932,13 +931,13 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2681
+          <t xml:space="preserve">3680
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">814
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -950,13 +949,13 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2635
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -974,7 +973,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -1004,7 +1003,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">9720
 </t>
         </is>
       </c>
@@ -1016,7 +1015,7 @@
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3124
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -1040,7 +1039,7 @@
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1064,13 +1063,13 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">454
+          <t xml:space="preserve">754
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1088,7 +1087,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">82182
 </t>
         </is>
       </c>
@@ -1106,7 +1105,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -1118,25 +1117,25 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">011
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -1196,7 +1195,7 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -1244,13 +1243,13 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">96811
+          <t xml:space="preserve">3680
 </t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
@@ -1268,7 +1267,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -1280,7 +1279,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -1292,7 +1291,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">008
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1316,7 +1315,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
@@ -1346,7 +1345,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">048
 </t>
         </is>
       </c>
@@ -1382,7 +1381,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -1400,7 +1399,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11850
+          <t xml:space="preserve">17830
 </t>
         </is>
       </c>
@@ -1418,7 +1417,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13549
+          <t xml:space="preserve">1345
 </t>
         </is>
       </c>
@@ -1430,7 +1429,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121008
+          <t xml:space="preserve">1008
 </t>
         </is>
       </c>
@@ -1460,13 +1459,13 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11080
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1484,7 +1483,7 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566
+          <t xml:space="preserve">85566
 </t>
         </is>
       </c>
@@ -1496,7 +1495,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1537905
+          <t xml:space="preserve">1275
 </t>
         </is>
       </c>
@@ -1514,25 +1513,25 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 2 20
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14200
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11395
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5891
+          <t xml:space="preserve">3891
 </t>
         </is>
       </c>
@@ -1556,13 +1555,13 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
+          <t xml:space="preserve">2567
 </t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8295
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -1586,11 +1585,16 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr"/>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">42
@@ -1599,13 +1603,13 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1175
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -1653,7 +1657,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1616
+          <t xml:space="preserve">6 1 6
 </t>
         </is>
       </c>
@@ -1671,19 +1675,19 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14178
+          <t xml:space="preserve">8778
 </t>
         </is>
       </c>
@@ -1713,13 +1717,13 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9353
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1892
 </t>
         </is>
       </c>
@@ -1731,37 +1735,37 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10104
+          <t xml:space="preserve">1004
 </t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2016
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -1809,7 +1813,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1563
+          <t xml:space="preserve">2563
 </t>
         </is>
       </c>
@@ -1845,7 +1849,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
@@ -1869,7 +1873,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
@@ -1899,13 +1903,13 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -1929,7 +1933,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -1953,7 +1957,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">25 8
 </t>
         </is>
       </c>
@@ -1965,7 +1969,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -1989,19 +1993,19 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1303
+          <t xml:space="preserve">303
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">7132
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -2019,7 +2023,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301
+          <t xml:space="preserve">2381
 </t>
         </is>
       </c>
@@ -2055,7 +2059,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2097,7 +2101,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -2145,13 +2149,13 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8008
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -2175,7 +2179,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8214
+          <t xml:space="preserve">12214
 </t>
         </is>
       </c>
@@ -2223,7 +2227,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2307,13 +2311,13 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
+          <t xml:space="preserve">851
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
@@ -2343,52 +2347,52 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">195
 </t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">821
-</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4080
-</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">194
@@ -2415,22 +2419,22 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">8300
+</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">300
 </t>
         </is>
       </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">300
-</t>
-        </is>
-      </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">710
@@ -2439,13 +2443,13 @@
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
@@ -2463,7 +2467,7 @@
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7166
+          <t xml:space="preserve">766
 </t>
         </is>
       </c>
@@ -2492,7 +2496,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15242
+          <t xml:space="preserve">1542
 </t>
         </is>
       </c>
@@ -2503,25 +2507,24 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5245
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -2533,25 +2536,25 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1624
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
+          <t xml:space="preserve">029
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11290
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
@@ -2575,13 +2578,13 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -2593,19 +2596,19 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2512
+          <t xml:space="preserve">2120
 </t>
         </is>
       </c>
@@ -2617,13 +2620,13 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138611
+          <t xml:space="preserve">3861
 </t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -2647,8 +2650,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2659,7 +2661,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -2689,7 +2691,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
@@ -2707,24 +2709,24 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38886</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9305
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -2742,13 +2744,13 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
+          <t xml:space="preserve">19662
 </t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -2766,13 +2768,13 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1412
+          <t xml:space="preserve">7722
 </t>
         </is>
       </c>
@@ -2801,12 +2803,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>324</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -2824,13 +2826,13 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11714
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>84</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2847,13 +2849,13 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1697
+          <t xml:space="preserve">1197
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -2895,7 +2897,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -2919,7 +2921,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -2931,8 +2933,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2979,7 +2980,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -3015,7 +3016,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -3033,13 +3034,13 @@
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1317
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2553
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -3057,19 +3058,19 @@
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -3105,7 +3106,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28990
+          <t xml:space="preserve">2990
 </t>
         </is>
       </c>
@@ -3123,7 +3124,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -3135,7 +3136,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -3219,13 +3220,13 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -3273,7 +3274,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3285,25 +3286,25 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18281
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -3333,13 +3334,13 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">8000
 </t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 0
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3387,19 +3388,19 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184841
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -3417,13 +3418,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9929
-</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -3441,13 +3441,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">1174
 </t>
         </is>
       </c>
@@ -3459,7 +3459,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">1891
 </t>
         </is>
       </c>
@@ -3489,19 +3489,19 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">048
 </t>
         </is>
       </c>
@@ -3585,25 +3585,25 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
+          <t xml:space="preserve">2258
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -3632,13 +3632,13 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 78
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16133
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3662,13 +3662,13 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12406
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153947
+          <t xml:space="preserve">11397
 </t>
         </is>
       </c>
@@ -3680,26 +3680,25 @@
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">796 1
+          <t xml:space="preserve">795 1
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406
-</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3710,7 +3709,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -3728,12 +3727,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9311
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -3763,17 +3762,17 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1019
-</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="n"/>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">197
@@ -3782,7 +3781,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -3800,67 +3799,68 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">03
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">640
+</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">844
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">053
 </t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">306
-</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">640
-</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">844
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
+          <t xml:space="preserve">1778
 </t>
         </is>
       </c>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -3913,8 +3913,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3931,14 +3930,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>41104</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3997,7 +3994,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -4033,13 +4030,13 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8450
+          <t xml:space="preserve">23450
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9317
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
@@ -4063,13 +4060,13 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18868
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4081,7 +4078,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4099,8 +4096,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -4109,15 +4105,10 @@
 </t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
+      <c r="P26" s="2" t="inlineStr"/>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3854
+          <t xml:space="preserve">884
 </t>
         </is>
       </c>
@@ -4189,13 +4180,13 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14182
+          <t xml:space="preserve">4182
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
@@ -4213,7 +4204,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1387
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -4225,7 +4216,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -4255,7 +4246,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -4309,13 +4300,12 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
-</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">8082
 </t>
         </is>
       </c>
@@ -4351,7 +4341,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326
+          <t xml:space="preserve">3256
 </t>
         </is>
       </c>
@@ -4375,7 +4365,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
@@ -4393,7 +4383,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">800
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4429,7 +4419,7 @@
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29798
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -4453,7 +4443,7 @@
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -4471,13 +4461,13 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26595
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1860
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
@@ -4500,8 +4490,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221121
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -4518,7 +4507,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2472
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -4542,20 +4531,20 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2189
 </t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241 9
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -4585,7 +4574,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -4603,7 +4592,7 @@
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2515
+          <t xml:space="preserve">1073
 </t>
         </is>
       </c>
@@ -4621,19 +4610,19 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -4649,21 +4638,15 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6251
-</t>
-        </is>
-      </c>
+      <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">565
-</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -4675,49 +4658,48 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5698
-</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">9228
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1148
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1237
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1802
+          <t xml:space="preserve">022
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
@@ -4729,25 +4711,25 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">755
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3121
+          <t xml:space="preserve">1220
 </t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01 35
+          <t xml:space="preserve">18 35
 </t>
         </is>
       </c>
@@ -4813,7 +4795,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212461
+          <t xml:space="preserve">513
 </t>
         </is>
       </c>
@@ -4825,19 +4807,14 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
-</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -4862,7 +4839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">20 2
 </t>
         </is>
       </c>
@@ -4910,19 +4887,19 @@
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
@@ -4934,13 +4911,13 @@
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1823
+          <t xml:space="preserve">823
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16828
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -4988,7 +4965,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -5000,7 +4977,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5084,19 +5061,19 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -5114,7 +5091,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
@@ -5126,57 +5103,58 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2006
+</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1225
+</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">206
 </t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1265
-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">241
@@ -5215,7 +5193,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
@@ -5251,7 +5229,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5281,7 +5259,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -5309,7 +5287,11 @@
 </t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">59
@@ -5342,7 +5324,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5366,13 +5348,13 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">802
+          <t xml:space="preserve">702
 </t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -5384,7 +5366,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -5396,13 +5378,13 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
+          <t xml:space="preserve">625
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -5474,7 +5456,7 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -5486,7 +5468,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189
+          <t xml:space="preserve">2149
 </t>
         </is>
       </c>
@@ -5522,7 +5504,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -5546,7 +5528,7 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">129593
+          <t xml:space="preserve">2953
 </t>
         </is>
       </c>
@@ -5558,7 +5540,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5576,7 +5558,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11172
+          <t xml:space="preserve">1172
 </t>
         </is>
       </c>
@@ -5600,7 +5582,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -5618,7 +5600,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5654,7 +5636,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -5682,12 +5664,7 @@
 </t>
         </is>
       </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
+      <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -5696,8 +5673,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>618</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
@@ -5714,7 +5690,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -5744,13 +5720,13 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">000
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11215
+          <t xml:space="preserve">1821
 </t>
         </is>
       </c>
@@ -5774,103 +5750,103 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18079
+</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1034
+</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0229
+</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">322
+</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 0
+</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1338
+</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1172
+</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
+</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39236
+</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">404
+</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1179
-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1034
-</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2331
-</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1272
-</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1363
-</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3936
-</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">404
-</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1241
-</t>
-        </is>
-      </c>
-      <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1298
-</t>
-        </is>
-      </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124660
+          <t xml:space="preserve">4160
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -5888,7 +5864,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1553
+          <t xml:space="preserve">1653
 </t>
         </is>
       </c>
@@ -5918,7 +5894,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">18 6
 </t>
         </is>
       </c>
@@ -5930,13 +5906,13 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">2 8
 </t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 1
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -5948,7 +5924,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -5972,7 +5948,7 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">2566
 </t>
         </is>
       </c>
@@ -5984,13 +5960,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>485</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8287
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>
@@ -6002,7 +5977,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -6014,13 +5989,13 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
@@ -6044,7 +6019,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3320
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -6074,19 +6049,19 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -6122,7 +6097,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">002
 </t>
         </is>
       </c>
@@ -6146,7 +6121,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66853
+          <t xml:space="preserve">665
 </t>
         </is>
       </c>
@@ -6170,7 +6145,7 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2178
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -6200,13 +6175,13 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2788
+          <t xml:space="preserve">27281
 </t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -6230,7 +6205,7 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -6242,7 +6217,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
@@ -6266,7 +6241,7 @@
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
@@ -6284,13 +6259,13 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">807
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -6308,7 +6283,7 @@
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
@@ -6338,7 +6313,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18114
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6356,7 +6331,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2486
+          <t xml:space="preserve">2426
 </t>
         </is>
       </c>
@@ -6404,7 +6379,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -6440,13 +6415,13 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2953
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -6458,7 +6433,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -6488,11 +6463,16 @@
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
-</t>
-        </is>
-      </c>
-      <c r="Z41" s="2" t="inlineStr"/>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>28</t>
@@ -6537,7 +6517,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1886
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -6549,7 +6529,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6567,7 +6547,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1812
 </t>
         </is>
       </c>
@@ -6585,7 +6565,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">808
 </t>
         </is>
       </c>
@@ -6633,13 +6613,13 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189535
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -6663,26 +6643,25 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3126
+          <t xml:space="preserve">3116
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>451</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -6693,13 +6672,13 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -6741,7 +6720,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -6789,12 +6768,12 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>854</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18495
+          <t xml:space="preserve">843
 </t>
         </is>
       </c>
@@ -6865,24 +6844,25 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9227
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t xml:space="preserve">1027
+</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101011
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121010
+          <t xml:space="preserve">1906
 </t>
         </is>
       </c>
@@ -6894,57 +6874,56 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">025
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1649
+          <t xml:space="preserve">18149
 </t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009001604
+          <t xml:space="preserve">1050816
 </t>
         </is>
       </c>
       <c r="M45" s="2" t="n"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">161285
+          <t xml:space="preserve">18205
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">49160
+          <t xml:space="preserve">4918
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">16 9
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12463
+          <t xml:space="preserve">8463
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1222
-</t>
+          <t>633</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -6967,30 +6946,31 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2220
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14124
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>39831</t>
+          <t xml:space="preserve">99295
+</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108209
+          <t xml:space="preserve">0805
 </t>
         </is>
       </c>
@@ -7014,7 +6994,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1305
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -7032,13 +7012,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1091
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
@@ -7056,7 +7036,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 5
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -7068,7 +7048,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -7092,7 +7072,7 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">2953
 </t>
         </is>
       </c>
@@ -7104,7 +7084,7 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2717
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -7116,37 +7096,37 @@
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2738
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
@@ -632,7 +632,8 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t xml:space="preserve">335
+</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -667,7 +668,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -691,7 +692,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -703,12 +704,13 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>061</t>
+          <t xml:space="preserve">07
+</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1330
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
@@ -720,7 +722,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -750,7 +752,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2921
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -760,7 +762,12 @@
 </t>
         </is>
       </c>
-      <c r="Z4" s="2" t="n"/>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1</t>
@@ -835,7 +842,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -853,7 +860,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 4
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -877,13 +884,13 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -907,7 +914,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1920
 </t>
         </is>
       </c>
@@ -931,7 +938,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">23680
 </t>
         </is>
       </c>
@@ -955,7 +962,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -973,7 +980,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1003,13 +1010,13 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9720
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -1033,7 +1040,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">596
 </t>
         </is>
       </c>
@@ -1069,7 +1076,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -1087,7 +1094,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">82182
+          <t xml:space="preserve">4182
 </t>
         </is>
       </c>
@@ -1117,7 +1124,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1129,13 +1136,13 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -1153,7 +1160,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -1171,7 +1178,7 @@
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -1213,7 +1220,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -1243,7 +1250,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">23680
 </t>
         </is>
       </c>
@@ -1255,7 +1262,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">2418
 </t>
         </is>
       </c>
@@ -1279,7 +1286,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -1315,13 +1322,13 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -1339,19 +1346,19 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
+          <t xml:space="preserve">548
 </t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">1230
 </t>
         </is>
       </c>
@@ -1369,7 +1376,7 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -1381,7 +1388,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1399,7 +1406,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17830
+          <t xml:space="preserve">17836
 </t>
         </is>
       </c>
@@ -1423,7 +1430,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">543
 </t>
         </is>
       </c>
@@ -1465,7 +1472,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">12 82
 </t>
         </is>
       </c>
@@ -1477,13 +1484,13 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85566
+          <t xml:space="preserve">2556
 </t>
         </is>
       </c>
@@ -1495,7 +1502,7 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">1375
 </t>
         </is>
       </c>
@@ -1513,7 +1520,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">1357
 </t>
         </is>
       </c>
@@ -1525,7 +1532,7 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">1395
 </t>
         </is>
       </c>
@@ -1537,7 +1544,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">1418
 </t>
         </is>
       </c>
@@ -1555,19 +1562,19 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2567
+          <t xml:space="preserve">3567
 </t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">323
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">2135
 </t>
         </is>
       </c>
@@ -1585,13 +1592,13 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -1603,13 +1610,13 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1633,7 +1640,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -1657,13 +1664,13 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6 1 6
+          <t xml:space="preserve">616
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -1687,13 +1694,13 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8778
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -1717,49 +1724,48 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1892
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
+          <t xml:space="preserve">1887
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1813,7 +1819,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2563
+          <t xml:space="preserve">563
 </t>
         </is>
       </c>
@@ -1843,13 +1849,13 @@
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">704
 </t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1867,7 +1873,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12182
+          <t xml:space="preserve">24182
 </t>
         </is>
       </c>
@@ -1897,19 +1903,19 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -1933,7 +1939,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">1233
 </t>
         </is>
       </c>
@@ -1957,7 +1963,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25 8
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -1975,7 +1981,7 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
@@ -1993,13 +1999,13 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">1303
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7132
+          <t xml:space="preserve">1732
 </t>
         </is>
       </c>
@@ -2023,7 +2029,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381
+          <t xml:space="preserve">2301
 </t>
         </is>
       </c>
@@ -2059,7 +2065,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -2089,7 +2095,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
@@ -2101,7 +2107,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -2161,7 +2167,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -2179,7 +2185,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12214
+          <t xml:space="preserve">1214
 </t>
         </is>
       </c>
@@ -2191,7 +2197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
@@ -2209,7 +2215,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1878
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
@@ -2245,7 +2251,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -2257,7 +2263,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 4
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -2311,13 +2317,13 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">1851
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
@@ -2335,7 +2341,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
+          <t xml:space="preserve">23408
 </t>
         </is>
       </c>
@@ -2377,7 +2383,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -2401,7 +2407,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
@@ -2419,7 +2425,7 @@
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8300
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -2449,13 +2455,13 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">250
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2419
 </t>
         </is>
       </c>
@@ -2473,7 +2479,8 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t xml:space="preserve">74
+</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2490,7 +2497,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153081
+          <t xml:space="preserve">15308
 </t>
         </is>
       </c>
@@ -2502,12 +2509,14 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t xml:space="preserve">997
+</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">2268
+</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2518,7 +2527,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">11921
 </t>
         </is>
       </c>
@@ -2542,19 +2551,19 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
+          <t xml:space="preserve">1029
 </t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -2578,13 +2587,13 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">1257
 </t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">1427
 </t>
         </is>
       </c>
@@ -2596,19 +2605,19 @@
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">763
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1365
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
@@ -2626,7 +2635,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">1423
 </t>
         </is>
       </c>
@@ -2644,13 +2653,14 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3062
+          <t xml:space="preserve">2306
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>304</t>
+          <t xml:space="preserve">308
+</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2661,7 +2671,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">954
 </t>
         </is>
       </c>
@@ -2691,7 +2701,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2721,7 +2731,8 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2744,7 +2755,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19662
+          <t xml:space="preserve">1662
 </t>
         </is>
       </c>
@@ -2774,13 +2785,13 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7722
+          <t xml:space="preserve">772
 </t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -2798,12 +2809,14 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33411</t>
+          <t xml:space="preserve">332
+</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t xml:space="preserve">322
+</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2814,30 +2827,31 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">1257
 </t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>84</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -2855,13 +2869,13 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
@@ -2873,7 +2887,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -2903,7 +2917,7 @@
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">1201
 </t>
         </is>
       </c>
@@ -2933,7 +2947,8 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">186
+</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2950,13 +2965,13 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">1322
 </t>
         </is>
       </c>
@@ -3016,7 +3031,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
@@ -3076,7 +3091,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
@@ -3112,7 +3127,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">1297
 </t>
         </is>
       </c>
@@ -3130,13 +3145,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1100
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">11184
 </t>
         </is>
       </c>
@@ -3160,19 +3175,19 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">11197
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
@@ -3262,7 +3277,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3575
+          <t xml:space="preserve">357
 </t>
         </is>
       </c>
@@ -3274,7 +3289,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
@@ -3292,7 +3307,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">1164
 </t>
         </is>
       </c>
@@ -3322,19 +3337,19 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">889
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8000
+          <t xml:space="preserve">16000
 </t>
         </is>
       </c>
@@ -3394,7 +3409,7 @@
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">18441
 </t>
         </is>
       </c>
@@ -3418,7 +3433,8 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t xml:space="preserve">2949
+</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3429,13 +3445,13 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">12380
 </t>
         </is>
       </c>
@@ -3447,7 +3463,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1174
+          <t xml:space="preserve">11674
 </t>
         </is>
       </c>
@@ -3471,7 +3487,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1891
+          <t xml:space="preserve">1191
 </t>
         </is>
       </c>
@@ -3483,7 +3499,7 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1221
 </t>
         </is>
       </c>
@@ -3495,13 +3511,13 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">000
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -3519,13 +3535,13 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">1668
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">048
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -3537,7 +3553,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
@@ -3549,7 +3565,7 @@
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
@@ -3573,7 +3589,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16101
+          <t xml:space="preserve">1610
 </t>
         </is>
       </c>
@@ -3585,13 +3601,13 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">0962
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2258
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
@@ -3603,7 +3619,8 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">882
+</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -3638,7 +3655,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1133
 </t>
         </is>
       </c>
@@ -3668,7 +3685,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11397
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
@@ -3680,25 +3697,26 @@
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">795 1
+          <t xml:space="preserve">796
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">1189
 </t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t xml:space="preserve">1406
+</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
@@ -3709,7 +3727,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
@@ -3727,7 +3745,8 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t xml:space="preserve">3220
+</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3738,7 +3757,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -3766,10 +3785,15 @@
 </t>
         </is>
       </c>
-      <c r="J24" s="2" t="n"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -3781,7 +3805,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
@@ -3793,7 +3817,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -3823,7 +3847,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">640
+          <t xml:space="preserve">1640
 </t>
         </is>
       </c>
@@ -3835,7 +3859,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -3913,7 +3937,8 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3930,12 +3955,13 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41104</t>
+          <t>406</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4944</t>
+          <t xml:space="preserve">198
+</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3994,7 +4020,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -4006,7 +4032,7 @@
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 52
+          <t xml:space="preserve">952
 </t>
         </is>
       </c>
@@ -4072,7 +4098,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -4096,7 +4122,8 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -4105,10 +4132,15 @@
 </t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">884
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
@@ -4120,7 +4152,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -4204,7 +4236,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -4216,7 +4248,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
@@ -4246,7 +4278,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -4300,12 +4332,13 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8082
+          <t xml:space="preserve">308
 </t>
         </is>
       </c>
@@ -4335,13 +4368,13 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2823
+          <t xml:space="preserve">2824
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3256
+          <t xml:space="preserve">1326
 </t>
         </is>
       </c>
@@ -4353,7 +4386,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">2682
 </t>
         </is>
       </c>
@@ -4365,7 +4398,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -4389,7 +4422,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">1201
 </t>
         </is>
       </c>
@@ -4455,13 +4488,13 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
@@ -4473,7 +4506,8 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">143
+</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4490,7 +4524,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>1462</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -4535,10 +4569,15 @@
 </t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2189
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -4574,7 +4613,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
@@ -4592,7 +4631,7 @@
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1073
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -4622,7 +4661,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4638,10 +4677,16 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1363
+</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3515</t>
+          <t xml:space="preserve">11565
+</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -4652,30 +4697,31 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11200
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t xml:space="preserve">2569
+</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9228
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">11718
 </t>
         </is>
       </c>
@@ -4687,19 +4733,19 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
+          <t xml:space="preserve">1022
 </t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1011
 </t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">1178
 </t>
         </is>
       </c>
@@ -4717,19 +4763,19 @@
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">755
+          <t xml:space="preserve">1455
 </t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 35
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4759,13 +4805,13 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">1337
 </t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4115
+          <t xml:space="preserve">24115
 </t>
         </is>
       </c>
@@ -4795,7 +4841,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">513
+          <t xml:space="preserve">1313
 </t>
         </is>
       </c>
@@ -4811,7 +4857,12 @@
 </t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">184
@@ -4826,11 +4877,16 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">204
@@ -4839,7 +4895,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20 2
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -4851,7 +4907,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -4887,19 +4943,19 @@
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">11138
 </t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1231
 </t>
         </is>
       </c>
@@ -4917,7 +4973,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4941,88 +4997,87 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1290
+</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1194
+</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1215
+</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">290
 </t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">245
@@ -5031,7 +5086,7 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">1279
 </t>
         </is>
       </c>
@@ -5055,25 +5110,25 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">1811
 </t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5091,7 +5146,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">481
+          <t xml:space="preserve">441
 </t>
         </is>
       </c>
@@ -5103,7 +5158,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2006
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -5127,19 +5182,19 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -5157,7 +5212,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
@@ -5193,7 +5248,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
@@ -5227,12 +5282,7 @@
 </t>
         </is>
       </c>
-      <c r="Z33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
+      <c r="Z33" s="2" t="inlineStr"/>
       <c r="AA33" t="inlineStr">
         <is>
           <t>22</t>
@@ -5265,7 +5315,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 9
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -5289,7 +5339,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -5300,19 +5350,19 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1201
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">201
 </t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
@@ -5468,7 +5518,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2149
+          <t xml:space="preserve">2139
 </t>
         </is>
       </c>
@@ -5480,7 +5530,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5528,13 +5578,13 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2953
+          <t xml:space="preserve">2093
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">1858
 </t>
         </is>
       </c>
@@ -5558,13 +5608,13 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">11172
 </t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
@@ -5582,13 +5632,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">11190
 </t>
         </is>
       </c>
@@ -5606,7 +5656,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -5624,7 +5674,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1258
 </t>
         </is>
       </c>
@@ -5664,7 +5714,12 @@
 </t>
         </is>
       </c>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -5673,7 +5728,8 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t xml:space="preserve">208
+</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
@@ -5684,13 +5740,13 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">1948
 </t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -5720,19 +5776,19 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1821
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">1429
 </t>
         </is>
       </c>
@@ -5750,13 +5806,13 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18079
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -5768,49 +5824,49 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0229
+          <t xml:space="preserve">1029
 </t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">4950
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 0
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1338
+          <t xml:space="preserve">1331
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">1179
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1363
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39236
+          <t xml:space="preserve">3936
 </t>
         </is>
       </c>
@@ -5822,19 +5878,19 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">1127
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
@@ -5864,7 +5920,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -5876,13 +5932,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 0 0
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5894,7 +5950,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18 6
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
@@ -5906,13 +5962,13 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 8
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -5924,7 +5980,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -5948,7 +6004,7 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2566
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -5960,24 +6016,25 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>485</t>
+          <t xml:space="preserve">273
+</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">788
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -5995,13 +6052,13 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">1832
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
@@ -6019,7 +6076,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">3323
 </t>
         </is>
       </c>
@@ -6043,7 +6100,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">1114
 </t>
         </is>
       </c>
@@ -6055,52 +6112,52 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">5 8
+</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">35
 </t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1000
-</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">002
-</t>
-        </is>
-      </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">307
@@ -6121,19 +6178,19 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">665
+          <t xml:space="preserve">685
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 78
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -6145,19 +6202,19 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">729
+          <t xml:space="preserve">1729
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6175,19 +6232,19 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">27281
+          <t xml:space="preserve">2781
 </t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">1308
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">12006
 </t>
         </is>
       </c>
@@ -6235,13 +6292,13 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -6277,7 +6334,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
+          <t xml:space="preserve">1654
 </t>
         </is>
       </c>
@@ -6295,7 +6352,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
@@ -6313,7 +6370,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1204
 </t>
         </is>
       </c>
@@ -6337,7 +6394,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">1296
 </t>
         </is>
       </c>
@@ -6367,16 +6424,11 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">118
@@ -6391,7 +6443,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -6433,7 +6485,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">7205
 </t>
         </is>
       </c>
@@ -6445,7 +6497,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">1271
 </t>
         </is>
       </c>
@@ -6457,19 +6509,19 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
+          <t xml:space="preserve">8411
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -6547,13 +6599,13 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1812
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
@@ -6565,7 +6617,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6607,13 +6659,13 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -6661,24 +6713,25 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t xml:space="preserve">259
+</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1086
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">416
 </t>
         </is>
       </c>
@@ -6708,7 +6761,7 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
@@ -6720,7 +6773,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6738,28 +6791,28 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1240
+</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">770
+</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">240
 </t>
         </is>
       </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">770
-</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">220
@@ -6768,7 +6821,8 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t xml:space="preserve">1252
+</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -6779,8 +6833,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6844,19 +6897,19 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">0527
 </t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1027
+          <t xml:space="preserve">8021
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">11278
 </t>
         </is>
       </c>
@@ -6874,13 +6927,13 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18149
+          <t xml:space="preserve">1149
 </t>
         </is>
       </c>
@@ -6892,14 +6945,19 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1050816
-</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="n"/>
+          <t xml:space="preserve">1038
+</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1029
+</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18205
+          <t xml:space="preserve">1205
 </t>
         </is>
       </c>
@@ -6911,24 +6969,25 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16 9
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8463
+          <t xml:space="preserve">1463
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t xml:space="preserve">1223
+</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1384
 </t>
         </is>
       </c>
@@ -6940,37 +6999,37 @@
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66 8
+          <t xml:space="preserve">1660
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
+          <t xml:space="preserve">12340
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">2190
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1381
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99295
+          <t xml:space="preserve">3923
 </t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0805
+          <t xml:space="preserve">380
 </t>
         </is>
       </c>
@@ -7012,13 +7071,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1091
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">1187
 </t>
         </is>
       </c>
@@ -7036,7 +7095,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -7048,7 +7107,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -7072,13 +7131,13 @@
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2953
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -7114,7 +7173,7 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">2276
 </t>
         </is>
       </c>
@@ -7126,7 +7185,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,146 +626,122 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3513
-</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
-</t>
+          <t>335</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
-</t>
+          <t>561</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -782,146 +758,122 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
-</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -938,146 +890,122 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23680
-</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">596
-</t>
+          <t>596</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
-</t>
+          <t>754</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1094,146 +1022,122 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
-</t>
+          <t>595</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1250,146 +1154,122 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23680
-</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2418
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
-</t>
+          <t>548</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1406,146 +1286,122 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17836
-</t>
+          <t>17836</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1617
-</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1074
-</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1345
-</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">543
-</t>
+          <t>543</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1008
-</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
-</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
-</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12 82
-</t>
+          <t>12 82</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4870
-</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2556
-</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
-</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1375
-</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3080
-</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
-</t>
+          <t>901</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
-</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
-</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1395
-</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3891
-</t>
+          <t>3891</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1418
-</t>
+          <t>418</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,146 +1418,122 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
-</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
-</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2135
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
-</t>
+          <t>974</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
-</t>
+          <t>616</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,8 +1550,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1729,134 +1560,112 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>332</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">563
-</t>
+          <t>563</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">704
-</t>
+          <t>704</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1873,146 +1682,122 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1303
-</t>
+          <t>303</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1732
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2029,146 +1814,122 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301
-</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
-</t>
+          <t>679</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
-</t>
+          <t>808</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2185,146 +1946,122 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
-</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1851
-</t>
+          <t>851</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2341,146 +2078,122 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23408
-</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>710</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2419
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
-</t>
+          <t>766</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>74</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2497,146 +2210,122 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15308
-</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1542
-</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
-</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2268
-</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>545</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11921
-</t>
+          <t>921</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
-</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4900
-</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1524
-</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
-</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1427
-</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
-</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">763
-</t>
+          <t>763</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1365
-</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400
-</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3861
-</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1423
-</t>
+          <t>423</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2653,146 +2342,122 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2306
-</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">954
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">772
-</t>
+          <t>772</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2809,146 +2474,122 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
-</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
-</t>
+          <t>776</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2965,146 +2606,122 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1322
-</t>
+          <t>322</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3121,146 +2738,122 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
-</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100
-</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">716
-</t>
+          <t>716</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3277,146 +2870,122 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">357
-</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
-</t>
+          <t>631</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18441
-</t>
+          <t>841</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3433,146 +3002,122 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2949
-</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12380
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11674
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">000
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
-</t>
+          <t>888</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3589,146 +3134,122 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
-</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1554
-</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0962
-</t>
+          <t>962</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
-</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4940
-</t>
+          <t>940</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1529
-</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3200
-</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
-</t>
+          <t>796</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
-</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
-</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406
-</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
-</t>
+          <t>4220</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3745,146 +3266,122 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
-</t>
+          <t>988</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1640
-</t>
+          <t>640</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>281</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">053
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3901,56 +3398,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
-</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3960,86 +3448,72 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">932
-</t>
+          <t>932</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
-</t>
+          <t>952</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -4056,146 +3530,122 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23450
-</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">552
-</t>
+          <t>552</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
-</t>
+          <t>743</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -4212,146 +3662,122 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>137</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
-</t>
+          <t>530</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4368,146 +3794,122 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2824
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2682
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4529,140 +3931,117 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
-</t>
+          <t>737</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4679,146 +4058,122 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1363
-</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11565
-</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2569
-</t>
+          <t>569</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
-</t>
+          <t>922</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11718
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1022
-</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1011
-</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4895
-</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1455
-</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3445
-</t>
+          <t>3445</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
-</t>
+          <t>688</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
-</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1153
-</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1337
-</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4835,146 +4190,122 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2727
-</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1313
-</t>
+          <t>313</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>979</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
-</t>
+          <t>689</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
-</t>
+          <t>823</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4991,14 +4322,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2635
-</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -5008,128 +4337,107 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">698
-</t>
+          <t>698</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1811
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -5146,140 +4454,117 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
-</t>
+          <t>441</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
-</t>
+          <t>834</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr"/>
@@ -5297,44 +4582,37 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
-</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -5344,98 +4622,82 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
-</t>
+          <t>702</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -5452,146 +4714,122 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2844
-</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1176
-</t>
+          <t>176</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2139
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>754</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2093
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1858
-</t>
+          <t>858</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5608,146 +4846,122 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11172
-</t>
+          <t>1172</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948
-</t>
+          <t>948</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5764,146 +4978,122 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8264
-</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
-</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
-</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
-</t>
+          <t>429</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
-</t>
+          <t>928</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1034
-</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
-</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
-</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4950
-</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1331
-</t>
+          <t>1331</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1179
-</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1363
-</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3936
-</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
-</t>
+          <t>404</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1127
-</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
-</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5920,146 +5110,122 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">788
-</t>
+          <t>787</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1832
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -6076,146 +5242,122 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3323
-</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5 8
-</t>
+          <t>0 08</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
-</t>
+          <t>665</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1729
-</t>
+          <t>729</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -6232,146 +5374,122 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
-</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12006
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1654
-</t>
+          <t>654</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
-</t>
+          <t>152</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
-</t>
+          <t>722</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1204
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -6388,141 +5506,118 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
-</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1296
-</t>
+          <t>296</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
+          <t>938</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">7205
-</t>
+          <t>705</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8411
-</t>
+          <t>811</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6539,146 +5634,122 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
-</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6695,140 +5766,117 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
-</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1086
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">416
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">843
-</t>
+          <t>843</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -6850,8 +5898,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
@@ -6891,146 +5938,122 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14234
-</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0527
-</t>
+          <t>1527</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8021
-</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11278
-</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1906
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">936
-</t>
+          <t>936</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1038
-</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1029
-</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205
-</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4918
-</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463
-</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
-</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1384
-</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414
-</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12340
-</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2190
-</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1381
-</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3923
-</t>
+          <t>923</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
-</t>
+          <t>380</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -7047,146 +6070,122 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
-</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>683</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>785</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">

--- a/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
@@ -1022,7 +1022,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>120</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>420</t>
+          <t>422</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>4182</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>219</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0 08</t>
+          <t>01 01</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>192</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>209</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">

--- a/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>180</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>420</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>192</t>
+          <t>199</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>180</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>128</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>282</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>01 01</t>
+          <t>0 01</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>002</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="2" t="n"/>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>138</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>385</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">

--- a/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
+++ b/results/05_transient_transcription_output/203/Midpoint_Excel_with_OCR_Results.xlsx
@@ -626,48 +626,49 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3513
+          <t xml:space="preserve">1862
 </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t xml:space="preserve">288
+</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">878
 </t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -679,91 +680,91 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">834
 </t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1220
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">743
+          <t xml:space="preserve">8118
 </t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">8
 </t>
         </is>
       </c>
@@ -781,144 +782,145 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
+          <t xml:space="preserve">4035
 </t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>311</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">326
+</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">254
 </t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">1566
 </t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">770
 </t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -936,49 +938,49 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">4223
 </t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">342
 </t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -990,92 +992,91 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">596
+          <t xml:space="preserve">552
 </t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1092,145 +1093,142 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
-</t>
+          <t>43351</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
+          <t xml:space="preserve">347
 </t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>433</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1021
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2351
 </t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3119
+          <t xml:space="preserve">342
 </t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">595
+          <t xml:space="preserve">506
 </t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -1248,142 +1246,146 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">2990
 </t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">806
 </t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">11190
+</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
+</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">206
 </t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">2409
 </t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t xml:space="preserve">965
+</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
+          <t xml:space="preserve">1214
 </t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">548
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="2" t="inlineStr"/>
+          <t xml:space="preserve">974
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>5</t>
@@ -1398,140 +1400,143 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">17836
+          <t xml:space="preserve">17835
 </t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1617
+          <t xml:space="preserve">1648
 </t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>014</t>
+          <t xml:space="preserve">969
+</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
+          <t xml:space="preserve">1308
 </t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">543
+          <t xml:space="preserve">679
 </t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">894
+</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
+          <t xml:space="preserve">1002
 </t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">996
+</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">1158
+</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">18945
 </t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1556
+          <t xml:space="preserve">1496
 </t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">1219
+</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">1357
+</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308 10
+          <t xml:space="preserve">2299
 </t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">901
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
+          <t xml:space="preserve">1328
 </t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t xml:space="preserve">1168
+</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">1335
 </t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3891
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">3888
+</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1552,117 +1557,122 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">323
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">8244
 </t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">616
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -1674,7 +1684,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">416
 </t>
         </is>
       </c>
@@ -1692,48 +1702,49 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4203
+          <t xml:space="preserve">2656
 </t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t xml:space="preserve">201
+</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1887
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">1866
 </t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -1745,90 +1756,91 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">11245
 </t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">0923
 </t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29332
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1255
 </t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">563
+          <t xml:space="preserve">706
 </t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1124
 </t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
+          <t xml:space="preserve">1271
 </t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">8249
 </t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>104</t>
+          <t xml:space="preserve">840
+</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -1846,143 +1858,145 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">3471
 </t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">27
+</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">1446
 </t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9233
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t xml:space="preserve">975
+</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1580
+          <t xml:space="preserve">578
 </t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">303
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
+          <t xml:space="preserve">767
 </t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -2000,145 +2014,145 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301
+          <t xml:space="preserve">14286
 </t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">966
 </t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">2221
 </t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
+          <t xml:space="preserve">527
 </t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">808
+          <t xml:space="preserve">776
 </t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2156,145 +2170,145 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">1903
 </t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">3207
 </t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1178
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">973
+</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">211
 </t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
-</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">273
-</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">242
 </t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">851
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -2312,145 +2326,146 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
+          <t xml:space="preserve">3596
 </t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">2088
 </t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">14196
 </t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1800
+</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">617
 </t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">250
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
+          <t xml:space="preserve">731
 </t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">09
+</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2465,143 +2480,100 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>53041</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15242
-</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">997
-</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1268
-</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">545
-</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">921
-</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0289
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">019
+          <t xml:space="preserve">1095
 </t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>097</t>
+          <t xml:space="preserve">1307
+</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4900
+          <t xml:space="preserve">4901
 </t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1524
+          <t xml:space="preserve">1487
 </t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t xml:space="preserve">1219
+</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">1361
+</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3310
+          <t xml:space="preserve">3318
 </t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1763
+          <t xml:space="preserve">766
 </t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1365
+          <t xml:space="preserve">1337
 </t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">1207
+</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">1425
+</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3861
-</t>
-        </is>
-      </c>
-      <c r="Z16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">4074
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2616,144 +2588,73 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3062
+          <t xml:space="preserve">15912
 </t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1055
 </t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1317
 </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">524
 </t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">368
 </t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">305
-</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">668
-</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>413</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="Z17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1106
+</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="n"/>
+      <c r="T17" s="2" t="n"/>
+      <c r="U17" s="2" t="n"/>
+      <c r="V17" s="2" t="n"/>
+      <c r="W17" s="2" t="n"/>
+      <c r="X17" s="2" t="n"/>
+      <c r="Y17" s="2" t="n"/>
+      <c r="Z17" s="2" t="n"/>
       <c r="AA17" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2768,142 +2669,139 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">3182
 </t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1197
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t xml:space="preserve">980
+</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">2722
 </t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>941</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t xml:space="preserve">815
+</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -2921,144 +2819,145 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3262
+          <t xml:space="preserve">3680
 </t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">8267
 </t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">8252
 </t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">8200
 </t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1257
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">717
 </t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -3076,145 +2975,144 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">2656
 </t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1884
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">976
 </t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">716
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>514</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3231,143 +3129,141 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3575
+          <t xml:space="preserve">3659
 </t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">314
 </t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
+          <t xml:space="preserve">623
 </t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t xml:space="preserve">273
+</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="Y21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">841
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="n"/>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t xml:space="preserve">91
+</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3384,145 +3280,145 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2949
+          <t xml:space="preserve">3408
 </t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3189
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1191
+          <t xml:space="preserve">8216
 </t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">000
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1668
+          <t xml:space="preserve">712
 </t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">7723
 </t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -3540,142 +3436,145 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16101
+          <t xml:space="preserve">3993
 </t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">150519
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">962
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">758
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">9728
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1227
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4940
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12529
+          <t xml:space="preserve">324
 </t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19116
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>39411</t>
+          <t xml:space="preserve">893
+</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3200
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18993
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>189</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t xml:space="preserve">297
+</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4220
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -3693,125 +3592,125 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
+          <t xml:space="preserve">17396
 </t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>037</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1324
 </t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">503
+</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11170
-</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">14894
 </t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1557
+</t>
+        </is>
+      </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">11468
 </t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">3957
 </t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">1344
 </t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1203
+</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>14081</t>
+        </is>
+      </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
-</t>
+          <t>39404</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -3829,122 +3728,145 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1778
+          <t xml:space="preserve">3439
 </t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">214
+</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t xml:space="preserve">101
+</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1018
+</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t xml:space="preserve">193
+</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1082
 </t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1070
 </t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">979
+</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr"/>
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">856
+</t>
+        </is>
+      </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t xml:space="preserve">651
+</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t xml:space="preserve">159
+</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">952
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
@@ -3962,147 +3884,122 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450
+          <t xml:space="preserve">1067
 </t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3117
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">21461
 </t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">552
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">53
 </t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
+          <t>2441</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr"/>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">743
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
           <t>17</t>
@@ -4117,144 +4014,134 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4182
+          <t xml:space="preserve">900
 </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>329</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2861
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">152
-</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
-</t>
+          <t>9240</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">12970
 </t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">530
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
+          <t xml:space="preserve">877
 </t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -4272,49 +4159,49 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2823
+          <t xml:space="preserve">3220
 </t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -4324,93 +4211,88 @@
 </t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12201
-</t>
-        </is>
-      </c>
+      <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1228
 </t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">732
 </t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4428,143 +4310,145 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1402
+          <t xml:space="preserve">29907
 </t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">312
+</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">602
+</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">286
 </t>
         </is>
       </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">737
-</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t xml:space="preserve">818
+</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -4582,138 +4466,143 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13635
-</t>
+          <t>34681</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">15065
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t xml:space="preserve">205
+</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">281
+</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1953
+</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8253
+</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">280
 </t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">569
-</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1022
-</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4895
-</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1455
-</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>35451</t>
-        </is>
-      </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3445
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">688
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>221</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4115
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -4731,140 +4620,140 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2727
+          <t xml:space="preserve">10562
 </t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">313
+          <t xml:space="preserve">1452
 </t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">032
 </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1192
 </t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
+          <t xml:space="preserve">1110
+</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">388
+</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">1065
 </t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">11592
 </t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">4876
 </t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">11858
 </t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">842
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">1409
 </t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
-</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">3968
+</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">1358
 </t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4882,7 +4771,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2635
+          <t xml:space="preserve">2112
 </t>
         </is>
       </c>
@@ -4894,125 +4783,127 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">966
 </t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">71
+</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr"/>
+          <t xml:space="preserve">975
+</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t xml:space="preserve">794
+</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">811
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -5030,143 +4921,145 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">441
+          <t xml:space="preserve">3847
 </t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>9521</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">1146
 </t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">1201
 </t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">8248
 </t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">8249
 </t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t xml:space="preserve">225
+</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>9481</t>
+          <t xml:space="preserve">249
+</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">52
+</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -5183,137 +5076,143 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">2133
+</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">516
+</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10214
+</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1235
+</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2846
+</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>9821</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">709
+</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">115
 </t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1178
-</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr"/>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1000
-</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">301
-</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">256
 </t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
-</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">702
-</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">746
 </t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
@@ -5331,145 +5230,138 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2844
+          <t xml:space="preserve">3116
 </t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">2114
+</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1267
+</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">188
 </t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
+      <c r="I35" s="2" t="inlineStr"/>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">8254
 </t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">11990
 </t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t xml:space="preserve">273
+</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>21382484</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
-</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5486,141 +5378,148 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1172
+          <t xml:space="preserve">3534
 </t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1311
 </t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">2466
 </t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">289
+</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="Z36" s="2" t="inlineStr"/>
+          <t xml:space="preserve">820
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>25</t>
@@ -5635,139 +5534,145 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8264
+          <t xml:space="preserve">4307
 </t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1429
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>00401</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t xml:space="preserve">265
+</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12034446</t>
+          <t xml:space="preserve">2410
+</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0444</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2149</t>
+          <t xml:space="preserve">251
+</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4950
+          <t xml:space="preserve">9725
 </t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1331
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">112879
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3936
+          <t xml:space="preserve">622
 </t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">404
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4160
+          <t xml:space="preserve">794
 </t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -5785,62 +5690,66 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1653
+          <t xml:space="preserve">16937
 </t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1554
 </t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>18871</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">534
 </t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">4
+</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">356
+</t>
+        </is>
+      </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">1060
 </t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">10159
 </t>
         </is>
       </c>
@@ -5852,67 +5761,73 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">11927
 </t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr"/>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1537
+</t>
+        </is>
+      </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">11431
 </t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">3248
 </t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">777
 </t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">1368
 </t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>465</t>
+          <t xml:space="preserve">1216
+</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>05</t>
+          <t xml:space="preserve">0011
+</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5929,133 +5844,140 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">3387
 </t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">193
 </t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1180
-</t>
-        </is>
-      </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1281
+</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">665
+          <t xml:space="preserve">650
 </t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">874
+</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">729
+          <t xml:space="preserve">982
 </t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -6073,74 +5995,80 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2781
+          <t xml:space="preserve">3325
 </t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">308
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="n"/>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9209
+</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">2148
 </t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t xml:space="preserve">990
+</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -6151,60 +6079,61 @@
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">654
+          <t xml:space="preserve">632
 </t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t xml:space="preserve">784
+</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">386
 </t>
         </is>
       </c>
@@ -6222,78 +6151,79 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2426
+          <t xml:space="preserve">4537
 </t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">1182
 </t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">9468
 </t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -6305,61 +6235,62 @@
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">8293
 </t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">705
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">982
 </t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">104
+</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -6376,68 +6307,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2886
+          <t xml:space="preserve">2656
 </t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">8256
 </t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1105
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>434</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="n"/>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">9286
 </t>
         </is>
       </c>
@@ -6449,63 +6384,70 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">8281
 </t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">220
 </t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
-        <is>
-          <t>843</t>
-        </is>
-      </c>
-      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>29</t>
@@ -6520,19 +6462,19 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
+          <t xml:space="preserve">2363
 </t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">1316
 </t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -6544,43 +6486,58 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0196
-</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="n"/>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">395
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9218
+</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="n"/>
+          <t xml:space="preserve">830
+</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1990
+</t>
+        </is>
+      </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">02
@@ -6589,44 +6546,59 @@
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">893
+</t>
+        </is>
+      </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
+          <t xml:space="preserve">977
 </t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr"/>
-      <c r="X43" s="2" t="inlineStr"/>
+          <t xml:space="preserve">859
+</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">282
+</t>
+        </is>
+      </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3923
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">323
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">905
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr"/>
       <c r="AA43" t="inlineStr">
         <is>
           <t>30</t>
@@ -6641,73 +6613,144 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>77797</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
-      <c r="E44" s="2" t="inlineStr"/>
-      <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr"/>
+          <t xml:space="preserve">3722
+</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">857
+</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1198
+</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1149
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1038
-</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="inlineStr"/>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4918
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">02
+</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">124612
-</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="n"/>
-      <c r="S44" s="2" t="n"/>
-      <c r="T44" s="2" t="n"/>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">304
+</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">756
+</t>
+        </is>
+      </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr"/>
-      <c r="W44" s="2" t="n"/>
-      <c r="X44" s="2" t="n"/>
-      <c r="Y44" s="2" t="n"/>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">847
+</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">780
+</t>
+        </is>
+      </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -6725,125 +6768,148 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
+          <t xml:space="preserve">3659
 </t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t xml:space="preserve">326
+</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1274
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t xml:space="preserve">194
+</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">823
 </t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">800
 </t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">785
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="2" t="n"/>
+          <t xml:space="preserve">844
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6856,95 +6922,129 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19016
+</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1216
+</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">1561
+</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">691
+</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>4274</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18259
+</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">848
+</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">59838
+</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1728
+</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">258
 </t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1187
-</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30
-</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41
-</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="n"/>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="n"/>
-      <c r="V46" s="2" t="n"/>
-      <c r="W46" s="2" t="n"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1449
+</t>
+        </is>
+      </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="2" t="n"/>
-      <c r="Z46" s="2" t="inlineStr"/>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5037
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -6957,9 +7057,135 @@
           <t>Tot.</t>
         </is>
       </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2376
+</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">317
+</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">860
+</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">750
+</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2141
+</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
